--- a/artfynd/A 34680-2026 artfynd.xlsx
+++ b/artfynd/A 34680-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136365887</v>
       </c>
       <c r="B3" t="n">
-        <v>92935</v>
+        <v>92938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>136365955</v>
       </c>
       <c r="B13" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>136365952</v>
       </c>
       <c r="B17" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 34680-2026 artfynd.xlsx
+++ b/artfynd/A 34680-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136365887</v>
       </c>
       <c r="B3" t="n">
-        <v>92938</v>
+        <v>92939</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>136365955</v>
       </c>
       <c r="B13" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>136365952</v>
       </c>
       <c r="B17" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 34680-2026 artfynd.xlsx
+++ b/artfynd/A 34680-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365940</v>
       </c>
       <c r="B2" t="n">
-        <v>83453</v>
+        <v>83455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136365887</v>
       </c>
       <c r="B3" t="n">
-        <v>92939</v>
+        <v>92944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>136365885</v>
       </c>
       <c r="B4" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136365943</v>
       </c>
       <c r="B5" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>136365954</v>
       </c>
       <c r="B6" t="n">
-        <v>79498</v>
+        <v>79500</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136365886</v>
       </c>
       <c r="B7" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>136365941</v>
       </c>
       <c r="B8" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136365942</v>
       </c>
       <c r="B9" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>136365945</v>
       </c>
       <c r="B10" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>136365956</v>
       </c>
       <c r="B12" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>136365955</v>
       </c>
       <c r="B13" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>136365951</v>
       </c>
       <c r="B14" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136365949</v>
       </c>
       <c r="B15" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>136365948</v>
       </c>
       <c r="B16" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>136365952</v>
       </c>
       <c r="B17" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 34680-2026 artfynd.xlsx
+++ b/artfynd/A 34680-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136365887</v>
       </c>
       <c r="B3" t="n">
-        <v>92944</v>
+        <v>92946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>136365955</v>
       </c>
       <c r="B13" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>136365952</v>
       </c>
       <c r="B17" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 34680-2026 artfynd.xlsx
+++ b/artfynd/A 34680-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365940</v>
       </c>
       <c r="B2" t="n">
-        <v>83455</v>
+        <v>83459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136365887</v>
       </c>
       <c r="B3" t="n">
-        <v>92946</v>
+        <v>92948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>136365885</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136365943</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>136365954</v>
       </c>
       <c r="B6" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>136365955</v>
       </c>
       <c r="B13" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>136365951</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136365949</v>
       </c>
       <c r="B15" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>136365952</v>
       </c>
       <c r="B17" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 34680-2026 artfynd.xlsx
+++ b/artfynd/A 34680-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365940</v>
       </c>
       <c r="B2" t="n">
-        <v>83459</v>
+        <v>83461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136365887</v>
       </c>
       <c r="B3" t="n">
-        <v>92948</v>
+        <v>92950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>136365885</v>
       </c>
       <c r="B4" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136365943</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>136365954</v>
       </c>
       <c r="B6" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>136365955</v>
       </c>
       <c r="B13" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>136365951</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136365949</v>
       </c>
       <c r="B15" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>136365952</v>
       </c>
       <c r="B17" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
